--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -2453,7 +2453,7 @@
         <v>136327182</v>
       </c>
       <c r="B19" t="n">
-        <v>87368</v>
+        <v>87370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>136327177</v>
       </c>
       <c r="B24" t="n">
-        <v>87410</v>
+        <v>87412</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136327181</v>
       </c>
       <c r="B25" t="n">
-        <v>87410</v>
+        <v>87412</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>136327187</v>
       </c>
       <c r="B91" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>136328907</v>
       </c>
       <c r="B94" t="n">
-        <v>87412</v>
+        <v>87414</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>136327186</v>
       </c>
       <c r="B106" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>136327171</v>
       </c>
       <c r="B161" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>136327168</v>
       </c>
       <c r="B169" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>136327174</v>
       </c>
       <c r="B264" t="n">
-        <v>90049</v>
+        <v>90051</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>136327185</v>
       </c>
       <c r="B269" t="n">
-        <v>87463</v>
+        <v>87465</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>136327179</v>
       </c>
       <c r="B271" t="n">
-        <v>87495</v>
+        <v>87497</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>136327173</v>
       </c>
       <c r="B279" t="n">
-        <v>87385</v>
+        <v>87387</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>136327175</v>
       </c>
       <c r="B282" t="n">
-        <v>93414</v>
+        <v>93417</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -11589,7 +11589,7 @@
         <v>136327186</v>
       </c>
       <c r="B106" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>136327168</v>
       </c>
       <c r="B169" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>136327175</v>
       </c>
       <c r="B282" t="n">
-        <v>93417</v>
+        <v>93418</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -2453,7 +2453,7 @@
         <v>136327182</v>
       </c>
       <c r="B19" t="n">
-        <v>87370</v>
+        <v>87372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>136327177</v>
       </c>
       <c r="B24" t="n">
-        <v>87412</v>
+        <v>87414</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136327181</v>
       </c>
       <c r="B25" t="n">
-        <v>87412</v>
+        <v>87414</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>136327187</v>
       </c>
       <c r="B91" t="n">
-        <v>91542</v>
+        <v>91544</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>136328907</v>
       </c>
       <c r="B94" t="n">
-        <v>87414</v>
+        <v>87416</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>136327186</v>
       </c>
       <c r="B106" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>136327171</v>
       </c>
       <c r="B161" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>136327168</v>
       </c>
       <c r="B169" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>136327174</v>
       </c>
       <c r="B264" t="n">
-        <v>90051</v>
+        <v>90053</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>136327185</v>
       </c>
       <c r="B269" t="n">
-        <v>87465</v>
+        <v>87467</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>136327179</v>
       </c>
       <c r="B271" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>136327173</v>
       </c>
       <c r="B279" t="n">
-        <v>87387</v>
+        <v>87389</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>136327175</v>
       </c>
       <c r="B282" t="n">
-        <v>93418</v>
+        <v>93423</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -2453,7 +2453,7 @@
         <v>136327182</v>
       </c>
       <c r="B19" t="n">
-        <v>87372</v>
+        <v>87374</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>136327177</v>
       </c>
       <c r="B24" t="n">
-        <v>87414</v>
+        <v>87416</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136327181</v>
       </c>
       <c r="B25" t="n">
-        <v>87414</v>
+        <v>87416</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>136327187</v>
       </c>
       <c r="B91" t="n">
-        <v>91544</v>
+        <v>91546</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>136328907</v>
       </c>
       <c r="B94" t="n">
-        <v>87416</v>
+        <v>87418</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>136327186</v>
       </c>
       <c r="B106" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>136327171</v>
       </c>
       <c r="B161" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>136327168</v>
       </c>
       <c r="B169" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>136327174</v>
       </c>
       <c r="B264" t="n">
-        <v>90053</v>
+        <v>90055</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>136327185</v>
       </c>
       <c r="B269" t="n">
-        <v>87467</v>
+        <v>87469</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>136327179</v>
       </c>
       <c r="B271" t="n">
-        <v>87499</v>
+        <v>87501</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>136327173</v>
       </c>
       <c r="B279" t="n">
-        <v>87389</v>
+        <v>87391</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>136327175</v>
       </c>
       <c r="B282" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -2453,7 +2453,7 @@
         <v>136327182</v>
       </c>
       <c r="B19" t="n">
-        <v>87374</v>
+        <v>87376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>136327177</v>
       </c>
       <c r="B24" t="n">
-        <v>87416</v>
+        <v>87418</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136327181</v>
       </c>
       <c r="B25" t="n">
-        <v>87416</v>
+        <v>87418</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>136327187</v>
       </c>
       <c r="B91" t="n">
-        <v>91546</v>
+        <v>91548</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>136328907</v>
       </c>
       <c r="B94" t="n">
-        <v>87418</v>
+        <v>87420</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>136327186</v>
       </c>
       <c r="B106" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>136327171</v>
       </c>
       <c r="B161" t="n">
-        <v>91628</v>
+        <v>91630</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>136327168</v>
       </c>
       <c r="B169" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>136327174</v>
       </c>
       <c r="B264" t="n">
-        <v>90055</v>
+        <v>90057</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>136327185</v>
       </c>
       <c r="B269" t="n">
-        <v>87469</v>
+        <v>87471</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>136327179</v>
       </c>
       <c r="B271" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>136327173</v>
       </c>
       <c r="B279" t="n">
-        <v>87391</v>
+        <v>87393</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>136327175</v>
       </c>
       <c r="B282" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
